--- a/attached_assets/Portal_Data_Latest_1763559925774.xlsx
+++ b/attached_assets/Portal_Data_Latest_1763559925774.xlsx
@@ -1,37 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PortalData\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{418E8E7D-78BB-4DDB-B6D7-C817AD5C172E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D4942E2D-ABEA-4B65-A960-7E9265DC1C6B}" activeTab="-1"/>
+    <workbookView/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -7657,7 +7633,7 @@
     <t>GCORE TECHNOLOGIES UK LIMITED</t>
   </si>
   <si>
-    <t>03/11 - Customer meeting, generating playbooks, followup on the 10/11</t>
+    <t>19/11 - Customer meeting review playbooks and campaign</t>
   </si>
   <si>
     <t>www.gcore.com</t>
@@ -17993,34 +17969,17 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="_-[$£-809]* #,##0.00_-;\-[$£-809]* #,##0.00_-;_-[$£-809]* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="00000000"/>
-  </numFmts>
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -18040,391 +17999,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" xfId="0" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <dxfs count="0"/>
 </styleSheet>
-</file>
-
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="0E2841"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="156082"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="E97132"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="196B24"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="A02B93"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="4EA72E"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="467886"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="96607D"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
-</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -18432,199 +18018,199 @@
   <dimension ref="A1:AV755"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="15.0296964645386" customWidth="1"/>
-    <col min="2" max="2" width="41.0534057617188" customWidth="1"/>
+    <col min="1" max="1" width="12.7932758331299" customWidth="1"/>
+    <col min="2" max="2" width="37.9351005554199" customWidth="1"/>
     <col min="3" max="3" width="9.140625" customWidth="1"/>
     <col min="4" max="4" width="9.140625" customWidth="1"/>
-    <col min="5" max="5" width="82.0721817016602" customWidth="1"/>
-    <col min="6" max="6" width="85.6355133056641" customWidth="1"/>
-    <col min="7" max="7" width="18.4477577209473" customWidth="1"/>
-    <col min="8" max="8" width="14.2460298538208" customWidth="1"/>
-    <col min="9" max="9" width="421.999938964844" customWidth="1"/>
-    <col min="10" max="10" width="32.0862426757813" customWidth="1"/>
-    <col min="11" max="11" width="17.8584728240967" customWidth="1"/>
-    <col min="12" max="12" width="15.813364982605" customWidth="1"/>
-    <col min="13" max="13" width="15.6537675857544" customWidth="1"/>
-    <col min="14" max="14" width="12.9313898086548" customWidth="1"/>
-    <col min="15" max="15" width="14.6133098602295" customWidth="1"/>
-    <col min="16" max="16" width="30.233470916748" customWidth="1"/>
-    <col min="17" max="17" width="33.8162460327148" customWidth="1"/>
-    <col min="18" max="18" width="140.580261230469" customWidth="1"/>
-    <col min="19" max="19" width="12.8966064453125" customWidth="1"/>
-    <col min="20" max="20" width="175.311264038086" customWidth="1"/>
-    <col min="21" max="21" width="12.4045114517212" customWidth="1"/>
-    <col min="22" max="22" width="114.406150817871" customWidth="1"/>
-    <col min="23" max="23" width="29.7516059875488" customWidth="1"/>
-    <col min="24" max="24" width="124.542686462402" customWidth="1"/>
-    <col min="25" max="25" width="29.5275554656982" customWidth="1"/>
-    <col min="26" max="26" width="141.866256713867" customWidth="1"/>
-    <col min="27" max="27" width="15.5023527145386" customWidth="1"/>
-    <col min="28" max="28" width="127.238464355469" customWidth="1"/>
-    <col min="29" max="29" width="12.1487445831299" customWidth="1"/>
-    <col min="30" max="30" width="90.9032745361328" customWidth="1"/>
-    <col min="31" max="31" width="38.7300224304199" customWidth="1"/>
-    <col min="32" max="32" width="39.5658683776855" customWidth="1"/>
-    <col min="33" max="33" width="32.9558486938477" customWidth="1"/>
-    <col min="34" max="34" width="53.9542579650879" customWidth="1"/>
-    <col min="35" max="35" width="54.0739555358887" customWidth="1"/>
-    <col min="36" max="36" width="34.1313514709473" customWidth="1"/>
-    <col min="37" max="37" width="87.9496917724609" customWidth="1"/>
-    <col min="38" max="38" width="54.0534973144531" customWidth="1"/>
-    <col min="39" max="39" width="253.536880493164" customWidth="1"/>
-    <col min="40" max="40" width="195.430877685547" customWidth="1"/>
-    <col min="41" max="41" width="237.690628051758" customWidth="1"/>
-    <col min="42" max="42" width="171.800094604492" customWidth="1"/>
-    <col min="43" max="43" width="183.934677124023" customWidth="1"/>
-    <col min="44" max="44" width="160.638458251953" customWidth="1"/>
-    <col min="45" max="45" width="328.634979248047" customWidth="1"/>
-    <col min="46" max="46" width="640.028442382813" customWidth="1"/>
-    <col min="47" max="47" width="157.320663452148" customWidth="1"/>
-    <col min="48" max="48" width="212.563125610352" customWidth="1"/>
+    <col min="5" max="5" width="67.9375152587891" customWidth="1"/>
+    <col min="6" max="6" width="70.4736938476563" customWidth="1"/>
+    <col min="7" max="7" width="16.6799030303955" customWidth="1"/>
+    <col min="8" max="8" width="13.4091625213623" customWidth="1"/>
+    <col min="9" max="9" width="381.066070556641" customWidth="1"/>
+    <col min="10" max="10" width="29.0896854400635" customWidth="1"/>
+    <col min="11" max="11" width="16.5868034362793" customWidth="1"/>
+    <col min="12" max="12" width="14.5365800857544" customWidth="1"/>
+    <col min="13" max="13" width="14.0322093963623" customWidth="1"/>
+    <col min="14" max="14" width="11.9165096282959" customWidth="1"/>
+    <col min="15" max="15" width="13.4429235458374" customWidth="1"/>
+    <col min="16" max="16" width="27.4896106719971" customWidth="1"/>
+    <col min="17" max="17" width="31.7250995635986" customWidth="1"/>
+    <col min="18" max="18" width="126.19596862793" customWidth="1"/>
+    <col min="19" max="19" width="11.4019079208374" customWidth="1"/>
+    <col min="20" max="20" width="145.692520141602" customWidth="1"/>
+    <col min="21" max="21" width="10.6571168899536" customWidth="1"/>
+    <col min="22" max="22" width="105.560737609863" customWidth="1"/>
+    <col min="23" max="23" width="25.4844017028809" customWidth="1"/>
+    <col min="24" max="24" width="115.341239929199" customWidth="1"/>
+    <col min="25" max="25" width="26.9709167480469" customWidth="1"/>
+    <col min="26" max="26" width="130.210479736328" customWidth="1"/>
+    <col min="27" max="27" width="13.3160629272461" customWidth="1"/>
+    <col min="28" max="28" width="117.715774536133" customWidth="1"/>
+    <col min="29" max="29" width="9.9992847442627" customWidth="1"/>
+    <col min="30" max="30" width="76.9251327514648" customWidth="1"/>
+    <col min="31" max="31" width="32.6192588806152" customWidth="1"/>
+    <col min="32" max="32" width="36.4189224243164" customWidth="1"/>
+    <col min="33" max="33" width="27.8548450469971" customWidth="1"/>
+    <col min="34" max="34" width="46.4234733581543" customWidth="1"/>
+    <col min="35" max="35" width="45.011646270752" customWidth="1"/>
+    <col min="36" max="36" width="28.5310916900635" customWidth="1"/>
+    <col min="37" max="37" width="71.1611938476563" customWidth="1"/>
+    <col min="38" max="38" width="45.6244583129883" customWidth="1"/>
+    <col min="39" max="39" width="206.104507446289" customWidth="1"/>
+    <col min="40" max="40" width="161.242065429688" customWidth="1"/>
+    <col min="41" max="41" width="197.691848754883" customWidth="1"/>
+    <col min="42" max="42" width="140.794082641602" customWidth="1"/>
+    <col min="43" max="43" width="150.329025268555" customWidth="1"/>
+    <col min="44" max="44" width="132.697540283203" customWidth="1"/>
+    <col min="45" max="45" width="270.274230957031" customWidth="1"/>
+    <col min="46" max="46" width="528.799743652344" customWidth="1"/>
+    <col min="47" max="47" width="129.508651733398" customWidth="1"/>
+    <col min="48" max="48" width="175.712295532227" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AA1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AB1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AC1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AE1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AF1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AG1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AH1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AI1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AK1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="2" t="s">
+      <c r="AM1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="2" t="s">
+      <c r="AN1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="2" t="s">
+      <c r="AO1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="2" t="s">
+      <c r="AP1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="2" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="2" t="s">
+      <c r="AR1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="2" t="s">
+      <c r="AS1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="2" t="s">
+      <c r="AT1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" s="2" t="s">
+      <c r="AU1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" s="2" t="s">
+      <c r="AV1" s="1" t="s">
         <v>47</v>
       </c>
     </row>

--- a/attached_assets/Portal_Data_Latest_1763559925774.xlsx
+++ b/attached_assets/Portal_Data_Latest_1763559925774.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <bookViews>
-    <workbookView/>
+    <workbookView activeTab="-1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
@@ -98,7 +98,7 @@
     <t>Why?4</t>
   </si>
   <si>
-    <t>AVERAGE</t>
+    <t>AV</t>
   </si>
   <si>
     <t>CEO</t>
@@ -18046,7 +18046,7 @@
     <col min="26" max="26" width="130.210479736328" customWidth="1"/>
     <col min="27" max="27" width="13.3160629272461" customWidth="1"/>
     <col min="28" max="28" width="117.715774536133" customWidth="1"/>
-    <col min="29" max="29" width="9.9992847442627" customWidth="1"/>
+    <col min="29" max="29" width="9.140625" customWidth="1"/>
     <col min="30" max="30" width="76.9251327514648" customWidth="1"/>
     <col min="31" max="31" width="32.6192588806152" customWidth="1"/>
     <col min="32" max="32" width="36.4189224243164" customWidth="1"/>

--- a/attached_assets/Portal_Data_Latest_1763559925774.xlsx
+++ b/attached_assets/Portal_Data_Latest_1763559925774.xlsx
@@ -98,7 +98,7 @@
     <t>Why?4</t>
   </si>
   <si>
-    <t>AV</t>
+    <t>AVERAGE</t>
   </si>
   <si>
     <t>CEO</t>
@@ -18046,7 +18046,7 @@
     <col min="26" max="26" width="130.210479736328" customWidth="1"/>
     <col min="27" max="27" width="13.3160629272461" customWidth="1"/>
     <col min="28" max="28" width="117.715774536133" customWidth="1"/>
-    <col min="29" max="29" width="9.140625" customWidth="1"/>
+    <col min="29" max="29" width="9.9992847442627" customWidth="1"/>
     <col min="30" max="30" width="76.9251327514648" customWidth="1"/>
     <col min="31" max="31" width="32.6192588806152" customWidth="1"/>
     <col min="32" max="32" width="36.4189224243164" customWidth="1"/>

--- a/attached_assets/Portal_Data_Latest_1763559925774.xlsx
+++ b/attached_assets/Portal_Data_Latest_1763559925774.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6036" uniqueCount="6036">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6037" uniqueCount="6037">
   <si>
     <t>HQ Country</t>
   </si>
@@ -18137,6 +18137,9 @@
   </si>
   <si>
     <t>CH62 1AA</t>
+  </si>
+  <si>
+    <t>NEC EUROPE LTD</t>
   </si>
 </sst>
 </file>
@@ -18195,7 +18198,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AV757"/>
+  <dimension ref="A1:AV758"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7932758331299" customWidth="1"/>
@@ -86500,6 +86503,32 @@
         <v>6035</v>
       </c>
     </row>
+    <row r="758">
+      <c r="B758" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="C758" s="0">
+        <v>778</v>
+      </c>
+      <c r="D758" s="0">
+        <v>1</v>
+      </c>
+      <c r="E758" s="0" t="s">
+        <v>6036</v>
+      </c>
+      <c r="F758" s="0" t="s">
+        <v>6036</v>
+      </c>
+      <c r="G758" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="J758" s="0">
+        <v>2832014</v>
+      </c>
+      <c r="K758" s="0" t="s">
+        <v>54</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="Q430" r:id="rId1"/>

--- a/attached_assets/Portal_Data_Latest_1763559925774.xlsx
+++ b/attached_assets/Portal_Data_Latest_1763559925774.xlsx
@@ -6505,7 +6505,7 @@
     <t>ELEVEN LABS LTD</t>
   </si>
   <si>
-    <t>Progressing</t>
+    <t>Gcore engaging at NAB</t>
   </si>
   <si>
     <t>www.elevenlabs.io</t>
@@ -18266,15 +18266,6 @@
     <t>EC2A 3AY</t>
   </si>
   <si>
-    <t>ePlus Ltd / IGX Global</t>
-  </si>
-  <si>
-    <t>ePlus Ltd</t>
-  </si>
-  <si>
-    <t>Meeting dates being scheduled for end of April</t>
-  </si>
-  <si>
     <t>WESCO ANIXTER</t>
   </si>
   <si>
@@ -18283,6 +18274,15 @@
   <si>
     <t xml:space="preserve">Face to face meeting with their team and nokias partner team. Strategic engagement in motion: strong alignment with Wesco on embedding Nokia as DC fabric, but still early and mostly at discussion/architecture level.
 Key gap remains structure: no defined EU commercial model yet and technical alignment still needs to be locked to move toward real opportunities.</t>
+  </si>
+  <si>
+    <t>ePlus Ltd / IGX Global</t>
+  </si>
+  <si>
+    <t>ePlus Ltd</t>
+  </si>
+  <si>
+    <t>Meeting dates being scheduled for end of April</t>
   </si>
 </sst>
 </file>
@@ -40738,7 +40738,7 @@
         <v>69</v>
       </c>
       <c r="L223" s="2">
-        <v>46351</v>
+        <v>46128</v>
       </c>
       <c r="M223" s="0" t="s">
         <v>2154</v>
@@ -89608,11 +89608,8 @@
       </c>
     </row>
     <row r="759">
-      <c r="B759" s="0" t="s">
-        <v>53</v>
-      </c>
       <c r="E759" s="0">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="F759" s="0">
         <v>1</v>
@@ -89627,18 +89624,21 @@
         <v>125</v>
       </c>
       <c r="K759" s="0" t="s">
-        <v>69</v>
+        <v>551</v>
       </c>
       <c r="L759" s="2">
-        <v>46120</v>
+        <v>46113</v>
       </c>
       <c r="M759" s="0" t="s">
         <v>6076</v>
       </c>
     </row>
     <row r="760">
+      <c r="B760" s="0" t="s">
+        <v>53</v>
+      </c>
       <c r="E760" s="0">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="F760" s="0">
         <v>1</v>
@@ -89653,10 +89653,10 @@
         <v>125</v>
       </c>
       <c r="K760" s="0" t="s">
-        <v>551</v>
+        <v>69</v>
       </c>
       <c r="L760" s="2">
-        <v>46113</v>
+        <v>46120</v>
       </c>
       <c r="M760" s="0" t="s">
         <v>6079</v>

--- a/attached_assets/Portal_Data_Latest_1763559925774.xlsx
+++ b/attached_assets/Portal_Data_Latest_1763559925774.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6110" uniqueCount="6110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6113" uniqueCount="6113">
   <si>
     <t>Category</t>
   </si>
@@ -18343,6 +18343,15 @@
   </si>
   <si>
     <t>Meeting dates being scheduled for May 22</t>
+  </si>
+  <si>
+    <t>https://chainergy.io</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C/O Addition Financial Limited, 1 Lyric Square, London, United Kingdom, </t>
+  </si>
+  <si>
+    <t>W6 0NB</t>
   </si>
   <si>
     <t>New one here :)</t>
@@ -89691,6 +89700,15 @@
       <c r="O760" s="0" t="s">
         <v>58</v>
       </c>
+      <c r="U760" s="3" t="s">
+        <v>6098</v>
+      </c>
+      <c r="V760" s="0" t="s">
+        <v>6099</v>
+      </c>
+      <c r="W760" s="0" t="s">
+        <v>6100</v>
+      </c>
     </row>
     <row r="761">
       <c r="E761" s="0">
@@ -89700,7 +89718,7 @@
         <v>1</v>
       </c>
       <c r="G761" s="0" t="s">
-        <v>6098</v>
+        <v>6101</v>
       </c>
     </row>
     <row r="762">
@@ -89717,10 +89735,10 @@
         <v>247</v>
       </c>
       <c r="G762" s="0" t="s">
-        <v>6099</v>
+        <v>6102</v>
       </c>
       <c r="H762" s="0" t="s">
-        <v>6100</v>
+        <v>6103</v>
       </c>
       <c r="I762" s="0" t="s">
         <v>125</v>
@@ -89732,16 +89750,16 @@
         <v>46139</v>
       </c>
       <c r="M762" s="0" t="s">
-        <v>6101</v>
+        <v>6104</v>
       </c>
       <c r="O762" s="0" t="s">
         <v>58</v>
       </c>
       <c r="U762" s="3" t="s">
-        <v>6102</v>
+        <v>6105</v>
       </c>
       <c r="V762" s="0" t="s">
-        <v>6103</v>
+        <v>6106</v>
       </c>
       <c r="W762" s="0" t="s">
         <v>4948</v>
@@ -89749,7 +89767,7 @@
     </row>
     <row r="763">
       <c r="B763" s="0" t="s">
-        <v>6104</v>
+        <v>6107</v>
       </c>
       <c r="C763" s="0" t="s">
         <v>691</v>
@@ -89761,10 +89779,10 @@
         <v>1</v>
       </c>
       <c r="G763" s="0" t="s">
-        <v>6105</v>
+        <v>6108</v>
       </c>
       <c r="H763" s="0" t="s">
-        <v>6106</v>
+        <v>6109</v>
       </c>
       <c r="I763" s="0" t="s">
         <v>125</v>
@@ -89776,7 +89794,7 @@
         <v>46141</v>
       </c>
       <c r="M763" s="0" t="s">
-        <v>6107</v>
+        <v>6110</v>
       </c>
       <c r="N763" s="0">
         <v>15339190</v>
@@ -89785,7 +89803,7 @@
         <v>58</v>
       </c>
       <c r="U763" s="3" t="s">
-        <v>6108</v>
+        <v>6111</v>
       </c>
       <c r="V763" s="0" t="s">
         <v>5809</v>
@@ -89802,7 +89820,7 @@
         <v>1</v>
       </c>
       <c r="G764" s="0" t="s">
-        <v>6109</v>
+        <v>6112</v>
       </c>
       <c r="I764" s="0" t="s">
         <v>125</v>
@@ -89814,7 +89832,7 @@
         <v>46143</v>
       </c>
       <c r="M764" s="0" t="s">
-        <v>6107</v>
+        <v>6110</v>
       </c>
     </row>
   </sheetData>
@@ -89824,8 +89842,9 @@
     <hyperlink ref="U753" r:id="rId3"/>
     <hyperlink ref="U754" r:id="rId4"/>
     <hyperlink ref="U755" r:id="rId5"/>
-    <hyperlink ref="U762" r:id="rId6"/>
-    <hyperlink ref="U763" r:id="rId7"/>
+    <hyperlink ref="U760" r:id="rId6"/>
+    <hyperlink ref="U762" r:id="rId7"/>
+    <hyperlink ref="U763" r:id="rId8"/>
   </hyperlinks>
   <headerFooter/>
 </worksheet>

--- a/attached_assets/Portal_Data_Latest_1763559925774.xlsx
+++ b/attached_assets/Portal_Data_Latest_1763559925774.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6113" uniqueCount="6113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6115" uniqueCount="6115">
   <si>
     <t>Category</t>
   </si>
@@ -3772,7 +3772,7 @@
     <t>CENTREQUARE</t>
   </si>
   <si>
-    <t>BROOKFIELD INFRASTRUCTURE</t>
+    <t>BROOKFIELD INFRASTRUCTURE/RADIANT</t>
   </si>
   <si>
     <t/>
@@ -18388,6 +18388,12 @@
   </si>
   <si>
     <t>Instadeep</t>
+  </si>
+  <si>
+    <t>KAO DATA LIMITED</t>
+  </si>
+  <si>
+    <t>invited to SReXperts</t>
   </si>
 </sst>
 </file>
@@ -18839,7 +18845,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AZ764"/>
+  <dimension ref="A1:AZ765"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="41.6263160705566" customWidth="1"/>
@@ -30769,10 +30775,10 @@
         <v>1242</v>
       </c>
       <c r="I121" s="0" t="s">
-        <v>55</v>
+        <v>125</v>
       </c>
       <c r="K121" s="0" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="L121" s="2">
         <v>45658</v>
@@ -38494,7 +38500,7 @@
         <v>199</v>
       </c>
       <c r="F199" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G199" s="0" t="s">
         <v>1939</v>
@@ -89833,6 +89839,29 @@
       </c>
       <c r="M764" s="0" t="s">
         <v>6110</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="E765" s="0">
+        <v>787</v>
+      </c>
+      <c r="F765" s="0">
+        <v>1</v>
+      </c>
+      <c r="G765" s="0" t="s">
+        <v>6113</v>
+      </c>
+      <c r="H765" s="0" t="s">
+        <v>6113</v>
+      </c>
+      <c r="K765" s="0" t="s">
+        <v>551</v>
+      </c>
+      <c r="L765" s="2">
+        <v>46176</v>
+      </c>
+      <c r="M765" s="0" t="s">
+        <v>6114</v>
       </c>
     </row>
   </sheetData>

--- a/attached_assets/Portal_Data_Latest_1763559925774.xlsx
+++ b/attached_assets/Portal_Data_Latest_1763559925774.xlsx
@@ -73354,7 +73354,7 @@
         <v>562</v>
       </c>
       <c r="F559" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G559" s="0" t="s">
         <v>4895</v>
